--- a/files/九龙-红磡-必嘉坊．迎汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．迎汇.xlsx
@@ -11467,7 +11467,7 @@
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>5356800</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>19550</v>
+        <v>19622</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>5356800</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>19550</v>
+        <v>19622</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
@@ -19759,9 +19759,9 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>D | 274呎 (1房)
+          <t>D | 273呎 (1房)
 $536万
-$19,550/呎
+$19,622/呎
 (23年-05月-22日)</t>
         </is>
       </c>

--- a/files/九龙-红磡-必嘉坊．迎汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．迎汇.xlsx
@@ -4098,14 +4098,14 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
-        <v>5520000</v>
+        <v>5924100</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>20444</v>
+        <v>21941</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>5520000</v>
+        <v>5924100</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>20444</v>
+        <v>21941</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
@@ -18777,9 +18777,9 @@
       <c r="G9" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
-$552万
-$20,444/呎
-(26年-09月-03日)</t>
+$592万
+$21,941/呎
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">

--- a/files/九龙-红磡-必嘉坊．迎汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．迎汇.xlsx
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>10206000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>27072</v>
+        <v>27144</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>10206000</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>27072</v>
+        <v>27144</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>11855600</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>29639</v>
+        <v>27700</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>11855600</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>29639</v>
+        <v>27700</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>4312000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>19336</v>
+        <v>19423</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>4312000</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>19336</v>
+        <v>19423</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>12093900</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>23483</v>
+        <v>23529</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>12093900</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>23483</v>
+        <v>23529</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>4298600</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>19276</v>
+        <v>19363</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>4298600</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>19276</v>
+        <v>19363</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>5516100</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>20205</v>
+        <v>20132</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>5516100</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>20205</v>
+        <v>20132</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>4286800</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>19223</v>
+        <v>19310</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>4286800</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>19223</v>
+        <v>19310</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>4274300</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>19167</v>
+        <v>19254</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>4274300</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>19167</v>
+        <v>19254</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>4261700</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>19111</v>
+        <v>19197</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>4261700</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>19111</v>
+        <v>19197</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>4249900</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>19058</v>
+        <v>19144</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>4249900</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>19058</v>
+        <v>19144</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>4237400</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>19002</v>
+        <v>19087</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>4237400</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>19002</v>
+        <v>19087</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>5617200</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>20576</v>
+        <v>20501</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>5617200</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>20576</v>
+        <v>20501</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>4225600</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>18949</v>
+        <v>19034</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>4225600</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>18949</v>
+        <v>19034</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>4212300</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>18889</v>
+        <v>18974</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>4212300</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>18889</v>
+        <v>18974</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>4200500</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>18836</v>
+        <v>18921</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>4200500</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>18836</v>
+        <v>18921</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>5356800</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>19622</v>
+        <v>19550</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>5356800</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>19622</v>
+        <v>19550</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="E188" s="4" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>5340600</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>19563</v>
+        <v>19491</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>5340600</v>
       </c>
       <c r="L188" s="5" t="n">
-        <v>19563</v>
+        <v>19491</v>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>5309100</v>
       </c>
       <c r="I214" s="5" t="n">
-        <v>19447</v>
+        <v>19376</v>
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>5309100</v>
       </c>
       <c r="L214" s="5" t="n">
-        <v>19447</v>
+        <v>19376</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="E217" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>4182400</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>18755</v>
+        <v>18840</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>4182400</v>
       </c>
       <c r="L217" s="5" t="n">
-        <v>18755</v>
+        <v>18840</v>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         </is>
       </c>
       <c r="E227" s="4" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>5675100</v>
       </c>
       <c r="I227" s="5" t="n">
-        <v>20788</v>
+        <v>20712</v>
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>5675100</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>20788</v>
+        <v>20712</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         </is>
       </c>
       <c r="E230" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>4117300</v>
       </c>
       <c r="I230" s="5" t="n">
-        <v>18463</v>
+        <v>18546</v>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>4117300</v>
       </c>
       <c r="L230" s="5" t="n">
-        <v>18463</v>
+        <v>18546</v>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         </is>
       </c>
       <c r="E240" s="4" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>5675100</v>
       </c>
       <c r="I240" s="5" t="n">
-        <v>20788</v>
+        <v>20712</v>
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>5675100</v>
       </c>
       <c r="L240" s="5" t="n">
-        <v>20788</v>
+        <v>20712</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         </is>
       </c>
       <c r="E243" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>4117300</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>18463</v>
+        <v>18546</v>
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>4117300</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>18463</v>
+        <v>18546</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="E272" s="4" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>3881800</v>
       </c>
       <c r="I272" s="5" t="n">
-        <v>20113</v>
+        <v>20218</v>
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>3881800</v>
       </c>
       <c r="L272" s="5" t="n">
-        <v>20113</v>
+        <v>20218</v>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="E275" s="4" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>5447700</v>
       </c>
       <c r="I275" s="5" t="n">
-        <v>23381</v>
+        <v>23481</v>
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>5447700</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>23381</v>
+        <v>23481</v>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         </is>
       </c>
       <c r="E278" s="4" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>5513000</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>23661</v>
+        <v>23763</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>5513000</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>23661</v>
+        <v>23763</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
@@ -18384,17 +18384,17 @@
       <c r="I5" s="21" t="inlineStr"/>
       <c r="J5" s="22" t="inlineStr">
         <is>
-          <t>J | 400呎 (2房)
+          <t>J | 428呎 (2房)
 $1186万
-$29,639/呎
+$27,700/呎
 (26年-06月-17日)</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr">
         <is>
-          <t>K | 377呎 (1房)
+          <t>K | 376呎 (1房)
 $1021万
-$27,072/呎
+$27,144/呎
 (26年-04月-29日)</t>
         </is>
       </c>
@@ -18431,9 +18431,9 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 223呎 (开放式)
+          <t>A | 222呎 (开放式)
 $431万
-$19,336/呎
+$19,423/呎
 (25年-12月-18日)</t>
         </is>
       </c>
@@ -18528,9 +18528,9 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>A | 223呎 (开放式)
+          <t>A | 222呎 (开放式)
 $430万
-$19,276/呎
+$19,363/呎
 (25年-12月-30日)</t>
         </is>
       </c>
@@ -18544,9 +18544,9 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>C | 515呎 (3房)
+          <t>C | 514呎 (3房)
 $1209万
-$23,483/呎
+$23,529/呎
 (24年-04月-08日)</t>
         </is>
       </c>
@@ -18625,9 +18625,9 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 223呎 (开放式)
+          <t>A | 222呎 (开放式)
 $429万
-$19,223/呎
+$19,310/呎
 (25年-12月-23日)</t>
         </is>
       </c>
@@ -18649,9 +18649,9 @@
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>D | 273呎 (1房)
+          <t>D | 274呎 (1房)
 $552万
-$20,205/呎
+$20,132/呎
 (23年-05月-16日)</t>
         </is>
       </c>
@@ -18736,9 +18736,9 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>A | 223呎 (开放式)
+          <t>A | 222呎 (开放式)
 $427万
-$19,167/呎
+$19,254/呎
 (26年-01月-09日)</t>
         </is>
       </c>
@@ -18847,9 +18847,9 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 223呎 (开放式)
+          <t>A | 222呎 (开放式)
 $426万
-$19,111/呎
+$19,197/呎
 (25年-12月-03日)</t>
         </is>
       </c>
@@ -18958,9 +18958,9 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>A | 223呎 (开放式)
+          <t>A | 222呎 (开放式)
 $425万
-$19,058/呎
+$19,144/呎
 (26年-01月-15日)</t>
         </is>
       </c>
@@ -19069,9 +19069,9 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>A | 223呎 (开放式)
+          <t>A | 222呎 (开放式)
 $424万
-$19,002/呎
+$19,087/呎
 (26年-01月-21日)</t>
         </is>
       </c>
@@ -19180,9 +19180,9 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>A | 223呎 (开放式)
+          <t>A | 222呎 (开放式)
 $423万
-$18,949/呎
+$19,034/呎
 (26年-01月-19日)</t>
         </is>
       </c>
@@ -19204,9 +19204,9 @@
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>D | 273呎 (1房)
+          <t>D | 274呎 (1房)
 $562万
-$20,576/呎
+$20,501/呎
 (23年-05月-24日)</t>
         </is>
       </c>
@@ -19291,9 +19291,9 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>A | 223呎 (开放式)
+          <t>A | 222呎 (开放式)
 $421万
-$18,889/呎
+$18,974/呎
 (26年-02月-04日)</t>
         </is>
       </c>
@@ -19402,9 +19402,9 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 223呎 (开放式)
+          <t>A | 222呎 (开放式)
 $420万
-$18,836/呎
+$18,921/呎
 (26年-02月-05日)</t>
         </is>
       </c>
@@ -19759,9 +19759,9 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>D | 273呎 (1房)
+          <t>D | 274呎 (1房)
 $536万
-$19,622/呎
+$19,550/呎
 (23年-05月-22日)</t>
         </is>
       </c>
@@ -19870,9 +19870,9 @@
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>D | 273呎 (1房)
+          <t>D | 274呎 (1房)
 $534万
-$19,563/呎
+$19,491/呎
 (23年-05月-18日)</t>
         </is>
       </c>
@@ -20068,9 +20068,9 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>A | 223呎 (开放式)
+          <t>A | 222呎 (开放式)
 $418万
-$18,755/呎
+$18,840/呎
 (25年-10月-24日)</t>
         </is>
       </c>
@@ -20092,9 +20092,9 @@
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>D | 273呎 (1房)
+          <t>D | 274呎 (1房)
 $531万
-$19,447/呎
+$19,376/呎
 (23年-05月-19日)</t>
         </is>
       </c>
@@ -20179,9 +20179,9 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>A | 223呎 (开放式)
+          <t>A | 222呎 (开放式)
 $412万
-$18,463/呎
+$18,546/呎
 (25年-10月-03日)</t>
         </is>
       </c>
@@ -20203,9 +20203,9 @@
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>D | 273呎 (1房)
+          <t>D | 274呎 (1房)
 $568万
-$20,788/呎
+$20,712/呎
 (23年-05月-18日)</t>
         </is>
       </c>
@@ -20290,9 +20290,9 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>A | 223呎 (开放式)
+          <t>A | 222呎 (开放式)
 $412万
-$18,463/呎
+$18,546/呎
 (25年-11月-03日)</t>
         </is>
       </c>
@@ -20314,9 +20314,9 @@
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>D | 273呎 (1房)
+          <t>D | 274呎 (1房)
 $568万
-$20,788/呎
+$20,712/呎
 (23年-05月-15日)</t>
         </is>
       </c>
@@ -20655,9 +20655,9 @@
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>E | 233呎 (1房)
+          <t>E | 232呎 (1房)
 $551万
-$23,661/呎
+$23,763/呎
 (23年-05月-29日)</t>
         </is>
       </c>
@@ -20679,9 +20679,9 @@
       </c>
       <c r="I26" s="22" t="inlineStr">
         <is>
-          <t>H | 233呎 (1房)
+          <t>H | 232呎 (1房)
 $545万
-$23,381/呎
+$23,481/呎
 (23年-07月-27日)</t>
         </is>
       </c>
@@ -20703,9 +20703,9 @@
       </c>
       <c r="L26" s="22" t="inlineStr">
         <is>
-          <t>L | 193呎 (开放式)
+          <t>L | 192呎 (开放式)
 $388万
-$20,113/呎
+$20,218/呎
 (25年-04月-07日)</t>
         </is>
       </c>
